--- a/output/roomself_excel/5909.xlsx
+++ b/output/roomself_excel/5909.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>82177</v>
+        <v>11684</v>
       </c>
       <c r="D2" t="n">
-        <v>3452</v>
+        <v>1200</v>
       </c>
       <c r="E2" t="n">
-        <v>610</v>
+        <v>46</v>
       </c>
       <c r="F2" t="n">
-        <v>389</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>131929</v>
+        <v>88740</v>
       </c>
       <c r="D3" t="n">
-        <v>2920</v>
+        <v>2564</v>
       </c>
       <c r="E3" t="n">
-        <v>735</v>
+        <v>369</v>
       </c>
       <c r="F3" t="n">
-        <v>269</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>41584</v>
+        <v>163374</v>
       </c>
       <c r="D4" t="n">
-        <v>1792</v>
+        <v>4316</v>
       </c>
       <c r="E4" t="n">
-        <v>184</v>
+        <v>670</v>
       </c>
       <c r="F4" t="n">
-        <v>18</v>
+        <v>353</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>144800</v>
+        <v>244392</v>
       </c>
       <c r="D5" t="n">
-        <v>3048</v>
+        <v>4060</v>
       </c>
       <c r="E5" t="n">
-        <v>418</v>
+        <v>439</v>
       </c>
       <c r="F5" t="n">
-        <v>381</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>306912</v>
+        <v>195911</v>
       </c>
       <c r="D6" t="n">
-        <v>9828</v>
+        <v>3552</v>
       </c>
       <c r="E6" t="n">
-        <v>939</v>
+        <v>409</v>
       </c>
       <c r="F6" t="n">
-        <v>851</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>11684</v>
+        <v>233273</v>
       </c>
       <c r="D7" t="n">
-        <v>1200</v>
+        <v>3864</v>
       </c>
       <c r="E7" t="n">
-        <v>46</v>
+        <v>487</v>
       </c>
       <c r="F7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
@@ -598,17 +598,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>48006</v>
+        <v>105154</v>
       </c>
       <c r="D8" t="n">
-        <v>1772</v>
+        <v>2660</v>
       </c>
       <c r="E8" t="n">
-        <v>189</v>
+        <v>259</v>
       </c>
       <c r="F8" t="n">
         <v>17</v>
@@ -624,16 +624,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>105154</v>
+        <v>94319</v>
       </c>
       <c r="D9" t="n">
-        <v>2660</v>
+        <v>2496</v>
       </c>
       <c r="E9" t="n">
-        <v>259</v>
+        <v>385</v>
       </c>
       <c r="F9" t="n">
-        <v>17</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10">
@@ -642,20 +642,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>432974</v>
+        <v>41584</v>
       </c>
       <c r="D10" t="n">
-        <v>8136</v>
+        <v>1792</v>
       </c>
       <c r="E10" t="n">
-        <v>1336</v>
+        <v>184</v>
       </c>
       <c r="F10" t="n">
-        <v>939</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11">
@@ -664,20 +664,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>58531</v>
+        <v>48006</v>
       </c>
       <c r="D11" t="n">
-        <v>2064</v>
+        <v>1772</v>
       </c>
       <c r="E11" t="n">
-        <v>73</v>
+        <v>189</v>
       </c>
       <c r="F11" t="n">
-        <v>67</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12">
@@ -686,20 +686,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>29412</v>
+        <v>40448</v>
       </c>
       <c r="D12" t="n">
-        <v>1428</v>
+        <v>1640</v>
       </c>
       <c r="E12" t="n">
-        <v>129</v>
+        <v>214</v>
       </c>
       <c r="F12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13">
@@ -708,20 +708,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>44128</v>
+        <v>218172</v>
       </c>
       <c r="D13" t="n">
-        <v>1808</v>
+        <v>7652</v>
       </c>
       <c r="E13" t="n">
-        <v>224</v>
+        <v>385</v>
       </c>
       <c r="F13" t="n">
-        <v>18</v>
+        <v>256</v>
       </c>
     </row>
     <row r="14">
@@ -730,20 +730,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>175570</v>
+        <v>44128</v>
       </c>
       <c r="D14" t="n">
-        <v>3388</v>
+        <v>1808</v>
       </c>
       <c r="E14" t="n">
-        <v>504</v>
+        <v>224</v>
       </c>
       <c r="F14" t="n">
-        <v>381</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15">
@@ -752,20 +752,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>195911</v>
+        <v>110185</v>
       </c>
       <c r="D15" t="n">
-        <v>3552</v>
+        <v>3180</v>
       </c>
       <c r="E15" t="n">
-        <v>812</v>
+        <v>601</v>
       </c>
       <c r="F15" t="n">
-        <v>293</v>
+        <v>244</v>
       </c>
     </row>
     <row r="16">
@@ -774,20 +774,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>233273</v>
+        <v>82177</v>
       </c>
       <c r="D16" t="n">
-        <v>3864</v>
+        <v>3452</v>
       </c>
       <c r="E16" t="n">
-        <v>938</v>
+        <v>389</v>
       </c>
       <c r="F16" t="n">
-        <v>487</v>
+        <v>253</v>
       </c>
     </row>
     <row r="17">
@@ -796,20 +796,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>94319</v>
+        <v>131929</v>
       </c>
       <c r="D17" t="n">
-        <v>2496</v>
+        <v>2920</v>
       </c>
       <c r="E17" t="n">
-        <v>385</v>
+        <v>329</v>
       </c>
       <c r="F17" t="n">
-        <v>275</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18">
@@ -822,16 +822,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>13968</v>
+        <v>144800</v>
       </c>
       <c r="D18" t="n">
-        <v>964</v>
+        <v>3048</v>
       </c>
       <c r="E18" t="n">
-        <v>144</v>
+        <v>418</v>
       </c>
       <c r="F18" t="n">
-        <v>19</v>
+        <v>381</v>
       </c>
     </row>
     <row r="19">
@@ -844,16 +844,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>69590</v>
+        <v>58531</v>
       </c>
       <c r="D19" t="n">
-        <v>3100</v>
+        <v>2064</v>
       </c>
       <c r="E19" t="n">
-        <v>344</v>
+        <v>73</v>
       </c>
       <c r="F19" t="n">
-        <v>243</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20">
@@ -866,16 +866,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>22127</v>
+        <v>29412</v>
       </c>
       <c r="D20" t="n">
-        <v>1312</v>
+        <v>1428</v>
       </c>
       <c r="E20" t="n">
-        <v>233</v>
+        <v>129</v>
       </c>
       <c r="F20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21">
@@ -884,20 +884,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>144881</v>
+        <v>25208</v>
       </c>
       <c r="D21" t="n">
-        <v>4280</v>
+        <v>1284</v>
       </c>
       <c r="E21" t="n">
-        <v>877</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -910,16 +910,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>45696</v>
+        <v>175570</v>
       </c>
       <c r="D22" t="n">
-        <v>1712</v>
+        <v>3388</v>
       </c>
       <c r="E22" t="n">
-        <v>634</v>
+        <v>504</v>
       </c>
       <c r="F22" t="n">
-        <v>535</v>
+        <v>381</v>
       </c>
     </row>
     <row r="23">
@@ -932,16 +932,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>44211</v>
+        <v>13968</v>
       </c>
       <c r="D23" t="n">
-        <v>2000</v>
+        <v>964</v>
       </c>
       <c r="E23" t="n">
-        <v>1017</v>
+        <v>144</v>
       </c>
       <c r="F23" t="n">
-        <v>362</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24">
@@ -954,16 +954,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>120206</v>
+        <v>69590</v>
       </c>
       <c r="D24" t="n">
-        <v>3764</v>
+        <v>3100</v>
       </c>
       <c r="E24" t="n">
-        <v>598</v>
+        <v>344</v>
       </c>
       <c r="F24" t="n">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="25">
@@ -976,15 +976,125 @@
         </is>
       </c>
       <c r="C25" t="n">
+        <v>22127</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1312</v>
+      </c>
+      <c r="E25" t="n">
+        <v>233</v>
+      </c>
+      <c r="F25" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>34696</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1580</v>
+      </c>
+      <c r="E26" t="n">
+        <v>276</v>
+      </c>
+      <c r="F26" t="n">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>45696</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1712</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>44211</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E28" t="n">
+        <v>237</v>
+      </c>
+      <c r="F28" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>79758</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2392</v>
+      </c>
+      <c r="E29" t="n">
+        <v>384</v>
+      </c>
+      <c r="F29" t="n">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
         <v>84146</v>
       </c>
-      <c r="D25" t="n">
+      <c r="D30" t="n">
         <v>2412</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E30" t="n">
         <v>236</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F30" t="n">
         <v>17</v>
       </c>
     </row>

--- a/output/roomself_excel/5909.xlsx
+++ b/output/roomself_excel/5909.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
         </is>
       </c>
     </row>
@@ -475,12 +495,20 @@
       <c r="D2" t="n">
         <v>1200</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>46</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>17</v>
       </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +525,20 @@
       <c r="D3" t="n">
         <v>2564</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
         <v>369</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>17</v>
       </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,11 +555,27 @@
       <c r="D4" t="n">
         <v>4316</v>
       </c>
-      <c r="E4" t="n">
-        <v>670</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>353</v>
+        <v>651</v>
+      </c>
+      <c r="G4" t="n">
+        <v>19</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>317</v>
+      </c>
+      <c r="J4" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="5">
@@ -541,12 +593,20 @@
       <c r="D5" t="n">
         <v>4060</v>
       </c>
-      <c r="E5" t="n">
-        <v>439</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>133</v>
-      </c>
+        <v>422</v>
+      </c>
+      <c r="G5" t="n">
+        <v>19</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +623,20 @@
       <c r="D6" t="n">
         <v>3552</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
         <v>409</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>18</v>
       </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,10 +653,26 @@
       <c r="D7" t="n">
         <v>3864</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>479</v>
+      </c>
+      <c r="G7" t="n">
+        <v>16</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
         <v>487</v>
       </c>
-      <c r="F7" t="n">
+      <c r="J7" t="n">
         <v>18</v>
       </c>
     </row>
@@ -607,11 +691,27 @@
       <c r="D8" t="n">
         <v>2660</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>259</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>17</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>406</v>
+      </c>
+      <c r="J8" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="9">
@@ -629,11 +729,27 @@
       <c r="D9" t="n">
         <v>2496</v>
       </c>
-      <c r="E9" t="n">
-        <v>385</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F9" t="n">
-        <v>275</v>
+        <v>257</v>
+      </c>
+      <c r="G9" t="n">
+        <v>18</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>367</v>
+      </c>
+      <c r="J9" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="10">
@@ -651,12 +767,20 @@
       <c r="D10" t="n">
         <v>1792</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
         <v>184</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>18</v>
       </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +797,20 @@
       <c r="D11" t="n">
         <v>1772</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
         <v>189</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>17</v>
       </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,12 +827,20 @@
       <c r="D12" t="n">
         <v>1640</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
         <v>214</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>17</v>
       </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,11 +857,27 @@
       <c r="D13" t="n">
         <v>7652</v>
       </c>
-      <c r="E13" t="n">
-        <v>385</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F13" t="n">
-        <v>256</v>
+        <v>367</v>
+      </c>
+      <c r="G13" t="n">
+        <v>17</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>239</v>
+      </c>
+      <c r="J13" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="14">
@@ -739,12 +895,20 @@
       <c r="D14" t="n">
         <v>1808</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
         <v>224</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>18</v>
       </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,11 +925,27 @@
       <c r="D15" t="n">
         <v>3180</v>
       </c>
-      <c r="E15" t="n">
-        <v>601</v>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F15" t="n">
-        <v>244</v>
+        <v>584</v>
+      </c>
+      <c r="G15" t="n">
+        <v>46</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>198</v>
+      </c>
+      <c r="J15" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="16">
@@ -783,11 +963,27 @@
       <c r="D16" t="n">
         <v>3452</v>
       </c>
-      <c r="E16" t="n">
-        <v>389</v>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F16" t="n">
-        <v>253</v>
+        <v>353</v>
+      </c>
+      <c r="G16" t="n">
+        <v>18</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>234</v>
+      </c>
+      <c r="J16" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="17">
@@ -805,12 +1001,20 @@
       <c r="D17" t="n">
         <v>2920</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
         <v>329</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>18</v>
       </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -827,11 +1031,27 @@
       <c r="D18" t="n">
         <v>3048</v>
       </c>
-      <c r="E18" t="n">
-        <v>418</v>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F18" t="n">
-        <v>381</v>
+        <v>362</v>
+      </c>
+      <c r="G18" t="n">
+        <v>18</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>400</v>
+      </c>
+      <c r="J18" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="19">
@@ -849,12 +1069,12 @@
       <c r="D19" t="n">
         <v>2064</v>
       </c>
-      <c r="E19" t="n">
-        <v>73</v>
-      </c>
-      <c r="F19" t="n">
-        <v>67</v>
-      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -871,12 +1091,20 @@
       <c r="D20" t="n">
         <v>1428</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
         <v>129</v>
       </c>
-      <c r="F20" t="n">
+      <c r="G20" t="n">
         <v>18</v>
       </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -893,12 +1121,12 @@
       <c r="D21" t="n">
         <v>1284</v>
       </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -915,11 +1143,27 @@
       <c r="D22" t="n">
         <v>3388</v>
       </c>
-      <c r="E22" t="n">
-        <v>504</v>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F22" t="n">
-        <v>381</v>
+        <v>485</v>
+      </c>
+      <c r="G22" t="n">
+        <v>19</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>362</v>
+      </c>
+      <c r="J22" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="23">
@@ -937,12 +1181,20 @@
       <c r="D23" t="n">
         <v>964</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
         <v>144</v>
       </c>
-      <c r="F23" t="n">
+      <c r="G23" t="n">
         <v>19</v>
       </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -959,11 +1211,27 @@
       <c r="D24" t="n">
         <v>3100</v>
       </c>
-      <c r="E24" t="n">
-        <v>344</v>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F24" t="n">
-        <v>243</v>
+        <v>311</v>
+      </c>
+      <c r="G24" t="n">
+        <v>17</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>226</v>
+      </c>
+      <c r="J24" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="25">
@@ -981,12 +1249,20 @@
       <c r="D25" t="n">
         <v>1312</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
         <v>233</v>
       </c>
-      <c r="F25" t="n">
+      <c r="G25" t="n">
         <v>17</v>
       </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1003,11 +1279,27 @@
       <c r="D26" t="n">
         <v>1580</v>
       </c>
-      <c r="E26" t="n">
-        <v>276</v>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F26" t="n">
-        <v>182</v>
+        <v>136</v>
+      </c>
+      <c r="G26" t="n">
+        <v>17</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>259</v>
+      </c>
+      <c r="J26" t="n">
+        <v>46</v>
       </c>
     </row>
     <row r="27">
@@ -1025,12 +1317,12 @@
       <c r="D27" t="n">
         <v>1712</v>
       </c>
-      <c r="E27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0</v>
-      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1047,12 +1339,12 @@
       <c r="D28" t="n">
         <v>2000</v>
       </c>
-      <c r="E28" t="n">
-        <v>237</v>
-      </c>
-      <c r="F28" t="n">
-        <v>19</v>
-      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1069,11 +1361,27 @@
       <c r="D29" t="n">
         <v>2392</v>
       </c>
-      <c r="E29" t="n">
-        <v>384</v>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F29" t="n">
-        <v>244</v>
+        <v>350</v>
+      </c>
+      <c r="G29" t="n">
+        <v>17</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>227</v>
+      </c>
+      <c r="J29" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="30">
@@ -1091,12 +1399,20 @@
       <c r="D30" t="n">
         <v>2412</v>
       </c>
-      <c r="E30" t="n">
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
         <v>236</v>
       </c>
-      <c r="F30" t="n">
+      <c r="G30" t="n">
         <v>17</v>
       </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
